--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
@@ -11,6 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,34 +30,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F6F7"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -73,27 +76,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -461,10 +472,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
@@ -509,18 +525,14 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Назначение: Подписание документов</t>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Назначение: Подписание документов. Источник правды: BPMN ump-signing-documents-ncins-pa.bpmn (PR NCINS). Timer PT25M.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -531,11 +543,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,12 +564,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1 Согласование</t>
         </is>
@@ -584,11 +600,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -604,7 +615,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -620,251 +631,253 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. Минимальная информация для определения необходимости проведения НТ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="126" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="98" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>[ump-signing-documents-ncins-pa]: Start → get-application-data → Connector передать управление (Kafka ump.process.to.system, messageName GenerateDocs) → stage SIGN_WAITING → Receive Message (ump.process.from.system, SigningDocs) → PUT /products/{id} (agreementLink) → End SUCCESS → main в оплату. Timer P25M → BANK_REJECT + delete.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Confluence to.system / from.system + BPMN</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>[ump-signing-documents-ncins-pa] (BPMN):
+1) Start → get-application-data (processType=SIGNING STATIC)
+2) Connector ump-process-transfer-connector → Kafka ump.process.to.system (systemCode=B2B STATIC, messageName=GenerateDocs STATIC, stopInIncident=true; applicationId=businessKey; correlationKey=businessKey+"."+productCode)
+3) kafka-product-stage-outbound-connector stage=SIGN_WAITING (STATIC)
+4) Receive Message SigningDocs; correlationKey = businessKey+"."+"NON_CREDIT_INSURANCE" (STATIC product в FEEL)
+5) update-product → End SUCCESS
+Event SubProcess Timer PT25M → status BANK_REJECT (forcefullyTerminate=true).
+Delete Call Activity в signing нет — cleanup делает main по timeoutMessage.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>BPMN + Confluence ump.process.to.system / from.system</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Sync-шаги: по стандарту / несколько секунд. Async в проде до 25 мин; для НТ сократить: бэкенд — несколько секунд, не более ~3 (уточнить у НТ). Таймер процесса подписания в доке — 25 мин.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>НТ async wait ≤ ~3 сек (TBD); прод до 25 мин</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Sync: несколько секунд. Async в проде до PT25M; для НТ сократить: несколько секунд, ≤~3 (TBD с НТ).</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>НТ async wait ≤~3 сек; прод PT25M</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>≈89/час среднее, ≈180/час макс (от 15000/мес). Дублей сообщений быть не должно.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>≈89/час среднее, ≈180/час макс (от 15000/мес). Дублей сообщений по задумке быть не должно.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>15000/мес</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="108" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>[GET /applications/{id}] ~89–180/час
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>[get-application-data] ~89–180/час
 [ump-process-transfer-connector / ump.process.to.system] ~89–180/час
-[kafka-product-stage-outbound-connector] SIGN_WAITING ~89–180/час
-[ump.process.from.system Receive SigningDocs] ~89–180/час (на НТ подкладываем)
-[PUT /products/{id}] ~89–180/час</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Ссылки: Confluence ump.process.to.system, ump.process.from.system</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+[kafka-product-stage SIGN_WAITING] ~89–180/час
+[Receive SigningDocs / ump.process.from.system] ~89–180/час (на НТ подкладываем)
+[update-product] ~89–180/час</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Ссылки Confluence to.system / from.system</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -880,7 +893,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -896,285 +909,579 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2. Полная информация для проведения НТ (заполняется, только если получено заключение от инженера о необходимости проведения НТ)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Старт из main: businessKey (DYNAMIC), productCode=NON_CREDIT_INSURANCE.
-Подписание сейчас моковое — готовых live JSON примеров сообщений бэкенд не дал (ждём аналитику).
-На НТ: после to.system нужно опубликовать completion в from.system (пока вручную). Автоматизацию — спросить у НТ.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Kafka publish completion с correlationKey=businessKey.productCode</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Старт из main Call Activity: businessKey, productCode=NON_CREDIT_INSURANCE.
+На НТ после to.system опубликовать SigningDocs в from.system с correlationKey = "&lt;businessKey&gt;.NON_CREDIT_INSURANCE".
+Live JSON примеров сообщений — TBD аналитика (подписание моковое).</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Kafka publish; correlationKey=businessKey.NON_CREDIT_INSURANCE</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Обычная ветка: result=SUCCESS → следующий процесс Оплата.
-Таймаут: BANK_REJECT; инстанс завершается/удаляется из Camunda; cleanup через мок AC.
-late-message: ничего не делаем; дубликатов быть не может.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Success: result=SUCCESS → main идёт в оплату (SIGN_COMPLETED).
+Timeout PT25M: BANK_REJECT; main получает timeoutMessage и вызывает delete.
+Late message после завершения — игнор; дубликатов быть не должно.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>SUCCESS vs BANK_REJECT</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Обновление стадии продукта (SIGN_WAITING) через Kafka; PUT продукта с agreementLink из сообщения. UMP сущности иначе — по маппингу update-product.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>stage + agreementLink у продукта</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Стадия SIGN_WAITING через Kafka; update-product (agreementLink из сообщения).</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>stage + agreementLink</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>HTTP signing-канал не мокается. Внешняя зависимость по факту — Kafka message flow: на НТ подкладываем completion message в топик (вручную). JSON-контракт сообщений — TBD аналитика.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Инструкция ручного/авто publish в Kafka</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>HTTP signing-канал не мокается. На НТ подкладываем completion в Kafka (вручную; автоматизация — с НТ). JSON-контракт — TBD.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Инструкция publish SigningDocs</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Для НТ не симулируем 1–25 мин реального подписания. Ожидание completion: несколько секунд, ≤~3 сек (уточнить с НТ).</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Не симулируем 1–25 мин. Completion на НТ: несколько секунд, ≤~3 (TBD).</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>≤3 сек на НТ</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>1) Success: get→to.system→SIGN_WAITING→подложить SigningDocs→PUT→SUCCESS→оплата.
-2) Timeout: не публиковать completion→timer→BANK_REJECT+delete.
-3) Late message после завершения — игнор.</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Два обязательных сценария: normal и timeout</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1) Success: get→to.system→SIGN_WAITING→подложить SigningDocs (corr=businessKey.NON_CREDIT_INSURANCE)→update-product→SUCCESS.
+2) Timeout: не публиковать → PT25M → BANK_REJECT; main → delete.
+3) Late message — игнор.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Normal + timeout</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>НТ пререквизиты :: Worker ump-signing-documents-ncins-pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Шаги из ump-signing-documents-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>BPMN id</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Type / called process</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Ключевые параметры</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>STATIC / DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>startEvent</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>businessKey, productCode</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC start</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>service-task-get-params</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Получить данные</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>processType=SIGNING</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>STATIC processType; DYNAMIC businessKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>transfer-connector</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Передать управление</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ump-process-transfer-connector → ump.process.to.system</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>systemCode=B2B; messageName=GenerateDocs; stopInIncident=true</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>STATIC codes; DYNAMIC applicationId/correlationKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>stage-connector</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>SIGN_WAITING</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>kafka-product-stage-outbound-connector</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>stage=SIGN_WAITING</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>STATIC stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>message-catch</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>SigningDocs</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>message intermediateCatch</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>correlationKey=businessKey+"."+"NON_CREDIT_INSURANCE"</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>STATIC product in FEEL; DYNAMIC businessKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>update-product</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Обновить продукт</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>type: update-product</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>agreementLink из сообщения</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>EventSubProcess</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>timer PT25M → BANK_REJECT</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>forcefullyTerminate=true</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>STATIC PT25M</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Методы и примеры (код)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +104,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -477,7 +478,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -493,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -525,10 +526,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Назначение: Подписание документов. Источник правды: BPMN ump-signing-documents-ncins-pa.bpmn (PR NCINS). Timer PT25M.</t>
+          <t>BPMN ump-signing-documents-ncins-pa (develop): get-application-data + connector transfer-control + message SigningDocs. В этом сервисе только ApplicationDataWorker.</t>
         </is>
       </c>
     </row>
@@ -548,7 +549,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -564,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -615,7 +616,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -631,7 +632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -674,204 +675,200 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="98" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>[ump-signing-documents-ncins-pa] (BPMN):
-1) Start → get-application-data (processType=SIGNING STATIC)
-2) Connector ump-process-transfer-connector → Kafka ump.process.to.system (systemCode=B2B STATIC, messageName=GenerateDocs STATIC, stopInIncident=true; applicationId=businessKey; correlationKey=businessKey+"."+productCode)
-3) kafka-product-stage-outbound-connector stage=SIGN_WAITING (STATIC)
-4) Receive Message SigningDocs; correlationKey = businessKey+"."+"NON_CREDIT_INSURANCE" (STATIC product в FEEL)
-5) update-product → End SUCCESS
-Event SubProcess Timer PT25M → status BANK_REJECT (forcefullyTerminate=true).
-Delete Call Activity в signing нет — cleanup делает main по timeoutMessage.</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>BPMN + Confluence ump.process.to.system / from.system</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>develop BPMN:
+1) get-application-data (SIGNING) → ApplicationDataWorker
+2) XOR: если systemCode="AlfaOffice" → End; иначе
+3) connector ump-process-transfer-connector.transfer-control.v1 (messageName=SigningDocs, useProcessInstanceKey=true, systemCode=productCode, stopInIncident=true)
+4) receiveTask SigningDocs, correlationKey=processInstanceKey
+В develop НЕТ update-product и НЕТ timer PT25M в этом BPMN (отличие от позднего PR).</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ump-signing-documents-ncins-pa.bpmn</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Sync: несколько секунд. Async в проде до PT25M; для НТ сократить: несколько секунд, ≤~3 (TBD с НТ).</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>НТ async wait ≤~3 сек; прод PT25M</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Sync get — несколько сек. Async wait SigningDocs — в проде до минут; на НТ сократить (≤~3 сек по СА).</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>≤~3 сек на НТ</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>≈89/час среднее, ≈180/час макс (от 15000/мес). Дублей сообщений по задумке быть не должно.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>15000/мес</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>База нагрузки СА: 15000 заявок/мес SFA → ≈89/час среднее, пик ≈180/час. Timeout-ветки ~5% (из них ~95% signing).</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>89 / 180</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>[get-application-data] ~89–180/час
-[ump-process-transfer-connector / ump.process.to.system] ~89–180/час
-[kafka-product-stage SIGN_WAITING] ~89–180/час
-[Receive SigningDocs / ump.process.from.system] ~89–180/час (на НТ подкладываем)
-[update-product] ~89–180/час</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Ссылки Confluence to.system / from.system</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>[get-application-data / GET applications] ~89–180
+[transfer-control connector / Kafka] ~89–180
+[Receive SigningDocs] ~89–180</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>внешний connector не в ump-ncins-pa</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -893,7 +890,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -909,7 +906,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -952,231 +949,231 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Старт из main Call Activity: businessKey, productCode=NON_CREDIT_INSURANCE.
-На НТ после to.system опубликовать SigningDocs в from.system с correlationKey = "&lt;businessKey&gt;.NON_CREDIT_INSURANCE".
-Live JSON примеров сообщений — TBD аналитика (подписание моковое).</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Kafka publish; correlationKey=businessKey.NON_CREDIT_INSURANCE</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Camunda: businessKey + processType=SIGNING.
+HTTP: GET /applications/{id}?include=PARTICIPANT&amp;include=PRODUCT
+Output SIGNING (маппер): processInstanceKey + getProcessParams.
+Далее внешний connector + message SigningDocs (corr=processInstanceKey в develop BPMN).
+Полный JSON Kafka — TBD (контракт аналитики / connector).</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorkerIT (processType можно SIGNING)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Success: result=SUCCESS → main идёт в оплату (SIGN_COMPLETED).
-Timeout PT25M: BANK_REJECT; main получает timeoutMessage и вызывает delete.
-Late message после завершения — игнор; дубликатов быть не должно.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SUCCESS vs BANK_REJECT</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Worker: getProcessParams=SUCCESS|ERROR. После message — End. AlfaOffice — короткий путь без connector.</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>SUCCESS / ERROR</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Стадия SIGN_WAITING через Kafka; update-product (agreementLink из сообщения).</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>stage + agreementLink</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>В ump-ncins-pa на signing update-product нет. Изменения стадии — через внешний connector/Kafka (вне репы).</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>UMP DB через этот сервис не меняется</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>HTTP signing-канал не мокается. На НТ подкладываем completion в Kafka (вручную; автоматизация — с НТ). JSON-контракт — TBD.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Инструкция publish SigningDocs</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Facade — стенд/WireMock. transfer-control + SigningDocs — подкладывать message в Zeebe/Kafka на НТ (JSON TBD).</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>corrKey=processInstanceKey (develop)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Не симулируем 1–25 мин. Completion на НТ: несколько секунд, ≤~3 (TBD).</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>≤3 сек на НТ</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>get sync несколько сек; message на НТ ≤~3 сек.</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>≤3 сек</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1) Success: get→to.system→SIGN_WAITING→подложить SigningDocs (corr=businessKey.NON_CREDIT_INSURANCE)→update-product→SUCCESS.
-2) Timeout: не публиковать → PT25M → BANK_REJECT; main → delete.
-3) Late message — игнор.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Normal + timeout</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>1) Success: get→transfer→подложить SigningDocs.
+2) AlfaOffice shortcut.
+3) Без message — зависание (timer в develop BPMN нет).</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Сверить с PR, если добавят timer/update-product</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -1193,15 +1190,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1214,14 +1211,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Шаги из ump-signing-documents-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+          <t>Методы signing (develop)</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1230,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN id</t>
+          <t>BPMN / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1243,241 +1240,113 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / called process</t>
+          <t>Type / HTTP</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ключевые параметры</t>
+          <t>Request / Input</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>STATIC / DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+          <t>Response / Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>startEvent</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>businessKey, productCode</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC start</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>processType=SIGNING</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>processInstanceKey, getProcessParams</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>service-task-get-params</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Получить данные</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>processType=SIGNING</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>STATIC processType; DYNAMIC businessKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>transfer-control.v1</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>внешний connector</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Kafka/connector</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>messageName=SigningDocs, useProcessInstanceKey=true</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>вне репы</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>transfer-connector</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Передать управление</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>ump-process-transfer-connector → ump.process.to.system</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>systemCode=B2B; messageName=GenerateDocs; stopInIncident=true</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>STATIC codes; DYNAMIC applicationId/correlationKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>stage-connector</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>SIGN_WAITING</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>kafka-product-stage-outbound-connector</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>stage=SIGN_WAITING</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>STATIC stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>message-catch</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SigningDocs</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>message intermediateCatch</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>correlationKey=businessKey+"."+"NON_CREDIT_INSURANCE"</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>STATIC product in FEEL; DYNAMIC businessKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>update-product</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Обновить продукт</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>type: update-product</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>agreementLink из сообщения</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>EventSubProcess</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>timer PT25M → BANK_REJECT</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>forcefullyTerminate=true</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>STATIC PT25M</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>message SigningDocs</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Zeebe receive</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>correlationKey=processInstanceKey</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>payload TBD</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>продолжение процесса</t>
         </is>
       </c>
     </row>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
@@ -885,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -906,7 +906,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row r="6" ht="220" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -962,21 +962,46 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Camunda: businessKey + processType=SIGNING.
-HTTP: GET /applications/{id}?include=PARTICIPANT&amp;include=PRODUCT
-Output SIGNING (маппер): processInstanceKey + getProcessParams.
-Далее внешний connector + message SigningDocs (corr=processInstanceKey в develop BPMN).
-Полный JSON Kafka — TBD (контракт аналитики / connector).</t>
+          <t xml:space="preserve">У воркера отсутствует HTTP-эндпоинт.
+Вызов происходит напрямую в Camunda.
+Camunda на базе Java скрипта, инструкция — https://confluence.moscow.alfaintra.net/pages/viewpage.action?pageId=2136656813
+Пример запроса:
+Map&lt;String, Object&gt; variables = Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110003", // id заявки (UMP application)
+  "productCode", "NON_CREDIT_INSURANCE" // const
+);
+final ProcessInstanceEvent processInstanceEvent = client
+  .newCreateInstanceCommand()
+  .bpmnProcessId("ump-signing-documents-ncins-pa")
+  .latestVersion()
+  .variables(variables)
+  .send()
+  .join();
+Параметры для запроса:
+1. businessKey — UUID заявки (параметризовать на объём ≥ ЧПН)
+2. productCode — const NON_CREDIT_INSURANCE (параметризация не нужна)
+--- Шаги ---
+1) ApplicationDataWorker
+Map.of("businessKey", "550e8400-e29b-41d4-a716-446655110003", "processType", "SIGNING");
+HTTP: GET .../applications/550e8400-e29b-41d4-a716-446655110003?include=PARTICIPANT&amp;include=PRODUCT
+2) Connector ump-process-transfer-connector.transfer-control.v1 (вне репы)
+messageName=SigningDocs, useProcessInstanceKey=true, systemCode=productCode
+3) Receive message SigningDocs
+correlationKey = processInstanceKey (develop BPMN)
+Полный JSON Kafka/message — TBD (в репе нет контракта; как в образце — добыть прогоном на стенде).
+</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>ApplicationDataWorkerIT (processType можно SIGNING)</t>
+          <t>Map.of start + GET applications; Kafka JSON TBD</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
+          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.
+Параметризовать businessKey (≥ ЧПН). productCode — const NON_CREDIT_INSURANCE.
+Источник примеров: develop ump-ncins-pa *WorkerIT + stubs.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -985,7 +1010,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="180" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -998,17 +1023,25 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Worker: getProcessParams=SUCCESS|ERROR. После message — End. AlfaOffice — короткий путь без connector.</t>
+          <t>Ответ HTTP у воркера signing (кроме get) отсутствует.
+get-application-data: getProcessParams = SUCCESS | ERROR; для SIGNING маппер отдаёт processInstanceKey.
+После message SigningDocs процесс идёт в End.
+Ветка systemCode="AlfaOffice" — End без connector.
+Ожидаемые коды/статусы для НТ:
+- SUCCESS (дошёл message)
+- зависание без message (в develop BPMN timer нет — сверить с PR)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SUCCESS / ERROR</t>
+          <t>getProcessParams=SUCCESS; message TBD</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
+          <t>Нужны примеры ответов, которые можно считать ожидаемыми.
+Например: getProcessParams=SUCCESS; HTTP 200/201; result=SUCCESS.
+Источник: *WorkerIT + stubs/ump/ump_application_response_200.json.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1179,6 +1212,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-signing-documents-ncins-pa.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -93,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +110,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -494,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -565,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -632,7 +639,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -885,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -906,7 +913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of) · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -1212,14 +1219,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1231,15 +1230,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1252,14 +1251,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>Полные request/response (не только имя метода). Источник: develop ump-ncins-pa@4a921a1653e + *WorkerIT + stubs. · полные HTTP body</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Методы signing (develop)</t>
+          <t>HTTP / JobWorker — полные тела запросов и ответов</t>
         </is>
       </c>
     </row>
@@ -1271,123 +1270,246 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN / JobWorker</t>
+          <t>Метод / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Где</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / HTTP</t>
+          <t>Полный REQUEST (headers + body)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Request / Input</t>
+          <t>Полный RESPONSE (status + body)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Response / Output</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="420" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>ApplicationDataWorker</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>GET /applications/{id}</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>processType=SIGNING</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>processInstanceKey, getProcessParams</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>transfer-control.v1</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>внешний connector</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Kafka/connector</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>messageName=SigningDocs, useProcessInstanceKey=true</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>вне репы</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>message SigningDocs</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Zeebe receive</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>correlationKey=processInstanceKey</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>payload TBD</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>продолжение процесса</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>get-application-data
+GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker
+все процессы</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>GET /applications/6dc5daf3-da12-4aae-9766-572da7b6b003?include=PARTICIPANT&amp;include=PRODUCT HTTP/1.1
+Host: ump-application-facade.ump.svc.cluster.local
+Accept: application/json
+(без body)
+Camunda job input:
+{
+  "businessKey": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "processType": "&lt;PREPARE_DOCUMENTS|SIGNING|PAYMENT|FINALISATION|DELETE_DOCS&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: application/json
+{
+  "externalApplicationIds": [
+    {
+      "extAppId": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+      "systemCode": "SFA",
+      "extAppCreateDate": "2026-06-25T12:45:34.785179Z"
+    }
+  ],
+  "channels": [
+    {
+      "id": "bd458000-77c2-48af-91b4-815f7ef2d4e6",
+      "userInfo": {
+        "userId": "f6753df0-b5c9-4828-a7b7-f9f3f7d8f33c",
+        "login": "service-account-nib-corp-ncins"
+      },
+      "code": "nib-corp-ncins",
+      "name": "НИБ. Страхование",
+      "isDeleted": false,
+      "category": "RECEIVE",
+      "type": "BANK_SYSTEM"
+    }
+  ],
+  "participants": [
+    {
+      "id": "bdec62a5-e10a-4c5b-86c7-b5ac190b8055",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "isDeleted": false,
+      "contacts": [
+        {
+          "type": "EMAIL",
+          "typeName": "Email",
+          "value": "romashka@rambler.ru",
+          "isPrimary": false
+        },
+        {
+          "type": "PHONE",
+          "typeName": "Телефон",
+          "value": "79183221488",
+          "isPrimary": false
+        }
+      ],
+      "addresses": [
+        {
+          "type": "FACT",
+          "typeName": "Адрес проживания / фактический - краткий",
+          "address": {
+            "fullAddress": "Г. Пушкино ул. Колотушкина д. 14/88"
+          }
+        }
+      ],
+      "identityDocuments": [],
+      "okveds": [],
+      "licenses": [],
+      "management": [],
+      "founders": [],
+      "externalPins": [],
+      "pin": "AAAXYX",
+      "type": "LEGAL",
+      "typeName": "Юридическое лицо",
+      "fullName": "ООО Звезда",
+      "inn": "7826688577",
+      "createDate": "2026-07-09T17:19:18.963685Z",
+      "lastUpdateDate": "2026-07-09T17:19:19.99786Z",
+      "citizenship": "Россия",
+      "citizenshipCode": "RU",
+      "taxCountryCode": "RU",
+      "ogrn": "1027810281740"
+    }
+  ],
+  "products": [
+    {
+      "id": "3d9fe175-2bc5-442a-b900-48522551de3f",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "status": {
+        "isTerminate": true,
+        "code": "COMPLETE",
+        "name": "Завершен"
+      },
+      "stage": {
+        "code": "PAYMENT_COMPLETED",
+        "name": "PAYMENT_COMPLETED"
+      },
+      "createDate": "2026-07-09T17:19:18.891861Z",
+      "lastUpdateDate": "2026-07-09T17:23:50.600316Z",
+      "code": "NON_CREDIT_INSURANCE",
+      "name": "Некредитное страхование ЮЛ",
+      "type": "PRODUCT",
+      "main": false,
+      "isDeleted": false,
+      "responsibleManager": {
+        "login": "U_M13RU"
+      },
+      "salesChannel": {
+        "code": "SFA",
+        "name": "SFA"
+      },
+      "productProperties": {
+        "programId": 1073741824,
+        "beginDate": "2026-06-25T11:47:13.57Z",
+        "endDate": "2026-06-25T11:47:13.57Z",
+        "signDate": "2026-06-25T11:47:13.57Z",
+        "duration": 12,
+        "insuranceSum": 20000.0,
+        "insurancePremium": 20000.0,
+        "contractNumber": "1423423/sdf/123",
+        "paymentType": "payment_account",
+        "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+        "insuranceObjects": [
+          {
+            "paymentAccount": "123523464567347"
+          }
+        ],
+        "code": "NON_CREDIT_INSURANCE"
+      },
+      "channelCode": "nib-corp-ncins"
+    }
+  ],
+  "options": [],
+  "id": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "createDate": "2026-07-09T17:19:18.833504Z",
+  "lastUpdateDate": "2026-07-09T17:22:46.462517Z",
+  "number": "UMP26070994592",
+  "statusCode": "COMPLETE",
+  "statusName": "Завершена",
+  "finalVersion": true,
+  "isDeleted": false
+}
+Camunda job output (успех):
+{ "getProcessParams": "SUCCESS", ...поля по processType из ApplicationMapper }
+Ошибка:
+{ "getProcessParams": "ERROR" }</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorkerIT
+stubs/ump/ump_application_response_200.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>ump-process-transfer-connector.transfer-control.v1</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>внешний connector
+signing</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Connector (вне ump-ncins-pa): ump-process-transfer-connector.transfer-control.v1
+BPMN inputs (develop):
+{
+  "stopInIncident": true,
+  "useProcessInstanceKey": true,
+  "systemCode": "&lt;productCode&gt;",
+  "messageName": "SigningDocs",
+  "applicationId": "&lt;businessKey&gt;"
+}
+Полный Kafka JSON to.system — TBD (внешний connector / аналитика).</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Далее receive message SigningDocs, correlationKey=processInstanceKey (develop).
+Payload from.system — TBD.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>BPMN signing
+(Kafka JSON TBD)</t>
         </is>
       </c>
     </row>
